--- a/tests_maj_split.xlsx
+++ b/tests_maj_split.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$909</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'多数与分歧'!$A$1:$H$412</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -120,6 +120,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -39745,7 +39746,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G555"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -50873,9 +50874,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="G336" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -58465,7 +58466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.21875" customWidth="1" min="1" max="1"/>
@@ -58476,7 +58477,7 @@
     <col width="18.21875" customWidth="1" min="6" max="6"/>
     <col width="35.6640625" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14.21875" customWidth="1" min="9" max="9"/>
+    <col width="16.21875" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -58625,6 +58626,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -58660,6 +58666,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="6" hidden="1">
       <c r="A6" t="n">
@@ -58730,6 +58741,11 @@
           <t>多数+分歧</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>["减:营业成本","税金及附加","销售费用","管理费用","研发费用","财务费用","其中:利息费用","利息收入","加：其他收益","投资收益","其中:对联营企业和合营企业的投资收益","以摊余成本计量的金融资产终止确认收益","净敞口套期收益","公允价值变动收益","信用减值损失","资产减值损失","资产处置收益"]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -58765,6 +58781,9 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>236222873.52</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -58915,6 +58934,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -58955,6 +58979,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="14" hidden="1">
       <c r="A14" t="n">
@@ -59195,6 +59224,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="20" hidden="1">
       <c r="A20" t="n">
@@ -59435,6 +59469,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -59475,6 +59514,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="27" hidden="1">
       <c r="A27" t="n">
@@ -59555,6 +59599,11 @@
           <t>多数</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="29" hidden="1">
       <c r="A29" t="n">
@@ -60765,6 +60814,11 @@
           <t>分歧</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
     </row>
     <row r="60" hidden="1">
       <c r="A60" t="n">
@@ -60883,6 +60937,11 @@
       <c r="H62" s="6" t="inlineStr">
         <is>
           <t>多数</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>√</t>
         </is>
       </c>
     </row>
